--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/NEW_HAMPSHIRE_2013.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/NEW_HAMPSHIRE_2013.xlsx
@@ -499,7 +499,7 @@
         <v>11</v>
       </c>
       <c r="D8">
-        <v>0.09090909090909099</v>
+        <v>0.09090909090909101</v>
       </c>
     </row>
     <row r="9">
